--- a/TestData/LoginData.xlsx
+++ b/TestData/LoginData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\autotest\eBankApp\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C92FE5-FABF-4D34-A8FA-17405B96A2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584D6C67-7325-417B-8D8E-45C991DAFD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>usename</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mngr588680</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tUhAnUm</t>
   </si>
   <si>
@@ -63,6 +59,18 @@
   </si>
   <si>
     <t>mngr5886</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mngr600390</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yzAbujU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alert</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -398,13 +406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -414,38 +422,50 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
+      <c r="D4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
